--- a/maverick-power-distribution/PCB/Project Outputs for MaverickPowerDistribution_v1.0/MaverickPowerDistribution_v1.0.xlsx
+++ b/maverick-power-distribution/PCB/Project Outputs for MaverickPowerDistribution_v1.0/MaverickPowerDistribution_v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Umich\arv\embedded_hardware\maverick-power-distribution\PCB\Project Outputs for MaverickPowerDistribution_v1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7C43F11-8122-4C3F-9974-4E85905E101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE5DFAFB-A17F-4D32-9DE5-BF0EF2A951EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1F53CBC2-D4ED-493E-906A-591E2786E580}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F66D340-E112-4393-A50A-A11A66845E75}"/>
   </bookViews>
   <sheets>
     <sheet name="MaverickPowerDistribution_v1.0" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="173">
   <si>
     <t>Comment</t>
   </si>
@@ -83,6 +83,18 @@
     <t>BEADC1608X95N</t>
   </si>
   <si>
+    <t>KT-0603R</t>
+  </si>
+  <si>
+    <t>Red 0603 Light Emitting Diodes</t>
+  </si>
+  <si>
+    <t>BLOWN_LEDA, BLOWN_LEDB</t>
+  </si>
+  <si>
+    <t>LED_KT-0603R</t>
+  </si>
+  <si>
     <t>CL05B103KB5NNNC</t>
   </si>
   <si>
@@ -128,7 +140,13 @@
     <t>Capacitor, Ceramic (MLCC), 100nF, ±10%, 16V, X7R, ±10%, SMD 0402</t>
   </si>
   <si>
-    <t>C6, C7, C18, C23</t>
+    <t>C6, C18</t>
+  </si>
+  <si>
+    <t>CAPC1005X60N</t>
+  </si>
+  <si>
+    <t>C7, C23</t>
   </si>
   <si>
     <t>CC0805KRX7R9BB104</t>
@@ -176,7 +194,10 @@
     <t>Capacitor, Ceramic (MLCC), 10uF, ±20%, 6.3V, X5R, ±20%, SMD 0402</t>
   </si>
   <si>
-    <t>C19, C20, C21</t>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20, C21</t>
   </si>
   <si>
     <t>885012106009</t>
@@ -203,7 +224,7 @@
     <t>C24</t>
   </si>
   <si>
-    <t>CAPC0603X33N</t>
+    <t>CAP-0603</t>
   </si>
   <si>
     <t>CL21A476MQYNNNE</t>
@@ -230,19 +251,16 @@
     <t>M7</t>
   </si>
   <si>
+    <t>LTST-C190GKT</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>LED RED CLEAR SMD</t>
-  </si>
-  <si>
-    <t>D_LED1, D_LED2, D_LEDA, D_LEDB</t>
-  </si>
-  <si>
-    <t>FP-AP2012EC-MFG</t>
-  </si>
-  <si>
-    <t>CMP-44529-000070-1</t>
+    <t>D_LED1, D_LED2</t>
+  </si>
+  <si>
+    <t>LEDM1608X80</t>
   </si>
   <si>
     <t>178.6165.0002</t>
@@ -275,7 +293,7 @@
     <t>CONN HEADER R/A 2POS</t>
   </si>
   <si>
-    <t>J1, J_MTR1A, J_MTR1B</t>
+    <t>J1_PWR, J_MTR1A, J_MTR1B</t>
   </si>
   <si>
     <t>FP-43045-0201-MFG</t>
@@ -299,6 +317,18 @@
     <t>CMP-02766-001412-1</t>
   </si>
   <si>
+    <t>PPTC041LFBN-RC</t>
+  </si>
+  <si>
+    <t>4 Position Header Connector 0.100 (2.54mm) Through Hole Tin</t>
+  </si>
+  <si>
+    <t>J_OLED</t>
+  </si>
+  <si>
+    <t>SULLINS_PPTC041LFBN-RC</t>
+  </si>
+  <si>
     <t>74439325056</t>
   </si>
   <si>
@@ -371,7 +401,7 @@
     <t>R1</t>
   </si>
   <si>
-    <t>RES-0603</t>
+    <t>RESC1607X60N</t>
   </si>
   <si>
     <t>0603WAF5103T5E</t>
@@ -422,15 +452,15 @@
     <t>R15, R16</t>
   </si>
   <si>
+    <t>Resistor, 1kΩ, ±1%, 100mW, 75V, ±100ppm/℃, -55℃~+155℃, SMD 0603</t>
+  </si>
+  <si>
+    <t>R17A, R17B</t>
+  </si>
+  <si>
     <t>0603WAF1001T5E</t>
   </si>
   <si>
-    <t>Resistor, 1kΩ, ±1%, 100mW, 75V, ±100ppm/℃, -55℃~+155℃, SMD 0603</t>
-  </si>
-  <si>
-    <t>R17A, R17B</t>
-  </si>
-  <si>
     <t>390kΩ</t>
   </si>
   <si>
@@ -446,33 +476,24 @@
     <t>0402WGF3903TCE</t>
   </si>
   <si>
-    <t>RES Thick Film, 100kΩ, 1%, 0.1W, 100ppm/°C, 0603</t>
+    <t>RC0603FR-07100KL</t>
+  </si>
+  <si>
+    <t>100 kOhms Â±1% 0.1W, 1/10W Chip Resistor 0603 (1608 Metric) Moisture Resistant Thick Film</t>
   </si>
   <si>
     <t>R21</t>
   </si>
   <si>
-    <t>FP-CRCW0603-e3-MFG</t>
-  </si>
-  <si>
-    <t>CMP-02407-005189-1</t>
-  </si>
-  <si>
-    <t>13K7 1% 2010(5025)</t>
-  </si>
-  <si>
-    <t>13K7 0.75W 1% 2010 (5025 Metric)  SMD</t>
+    <t>0603WAF1302T5E</t>
+  </si>
+  <si>
+    <t>Resistor, 13kΩ, ±1%, 100mW, 75V, ±100ppm/℃, -55℃~+155℃, SMD 0603</t>
   </si>
   <si>
     <t>R22</t>
   </si>
   <si>
-    <t>RESC2010(5025)_N</t>
-  </si>
-  <si>
-    <t>CMP-1017-00637-1</t>
-  </si>
-  <si>
     <t>0603WAF1002T5E</t>
   </si>
   <si>
@@ -506,7 +527,7 @@
     <t>ACS711KEXLT-15AB-T</t>
   </si>
   <si>
-    <t>Current Sensor 31A 1 Channel Hall Effect, Open Loop Bidirectional 12-PowerWFQFN</t>
+    <t>Current Sensor 15.5A 1 Channel Hall Effect, Open Loop Bidirectional 12-PowerWFQFN</t>
   </si>
   <si>
     <t>U2A, U2B</t>
@@ -515,16 +536,16 @@
     <t>XDCR_ACS711KEXLT-15AB-T</t>
   </si>
   <si>
-    <t>IC REG BUCK ADJ 2A TSOT23-6</t>
+    <t>TPS561201DDCT</t>
+  </si>
+  <si>
+    <t>4.5V to 17V Input, 1A Synchronous Step-Down Voltage Regulator in 6-pin SOT-23</t>
   </si>
   <si>
     <t>U3</t>
   </si>
   <si>
-    <t>FP-DDC0006A-IPC_A</t>
-  </si>
-  <si>
-    <t>CMP-04918-000439-1</t>
+    <t>SOT95P280X110-6N</t>
   </si>
   <si>
     <t>32.768kHz</t>
@@ -932,11 +953,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{510C3275-E113-4857-B7CA-059248289A65}">
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6969CD-20F8-45A6-983B-B0FD8107082F}">
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="6" width="17.33203125" customWidth="1"/>
+    <col min="1" max="6" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="4" customFormat="1">
@@ -1016,7 +1037,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1030,30 +1051,30 @@
         <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1061,19 +1082,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1081,39 +1102,39 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F9" s="1">
         <v>2</v>
@@ -1121,19 +1142,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
@@ -1141,7 +1162,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>37</v>
@@ -1153,10 +1174,10 @@
         <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1170,7 +1191,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>40</v>
@@ -1184,19 +1205,19 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1210,30 +1231,30 @@
         <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -1241,99 +1262,99 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F20" s="1">
         <v>2</v>
@@ -1341,99 +1362,99 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
@@ -1441,17 +1462,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="C26" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
@@ -1459,39 +1482,39 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
@@ -1499,19 +1522,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F29" s="1">
         <v>1</v>
@@ -1519,19 +1542,17 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>115</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B30" s="1"/>
       <c r="C30" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
@@ -1539,157 +1560,159 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F31" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1"/>
-      <c r="B36" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F38" s="1">
         <v>2</v>
@@ -1697,39 +1720,39 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -1737,57 +1760,139 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1"/>
-      <c r="B42" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E45" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F43" s="1">
+      <c r="B46" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="1">
         <v>1</v>
       </c>
     </row>
